--- a/diseases/d057/2020-2025.xlsx
+++ b/diseases/d057/2020-2025.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1658,6 +1663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2395,6 +2405,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3132,6 +3147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4017,6 +4037,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4754,6 +4779,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5491,6 +5521,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6376,6 +6411,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7113,6 +7153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7850,6 +7895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8735,6 +8785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9472,6 +9527,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10357,6 +10417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11094,6 +11159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11831,6 +11901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12568,6 +12643,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13453,6 +13533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14190,6 +14275,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14927,6 +15017,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15812,6 +15907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16549,6 +16649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17434,6 +17539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18171,6 +18281,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18908,6 +19023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19793,6 +19913,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20530,6 +20655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21267,6 +21397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22152,6 +22287,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22889,6 +23029,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23626,6 +23771,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24511,6 +24661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25248,6 +25403,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25985,6 +26145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26870,6 +27035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27607,6 +27777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28344,6 +28519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29229,6 +29409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29966,6 +30151,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30703,6 +30893,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31588,6 +31783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32325,6 +32525,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33062,6 +33267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33947,6 +34157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34684,6 +34899,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35569,6 +35789,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36306,6 +36531,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37043,6 +37273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37928,6 +38163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38665,6 +38905,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39402,6 +39647,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40287,6 +40537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41024,6 +41279,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41761,6 +42021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42646,6 +42911,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43383,6 +43653,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44120,6 +44395,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45005,6 +45285,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45742,6 +46027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46627,6 +46917,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47364,6 +47659,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48101,6 +48401,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48986,6 +49291,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49723,6 +50033,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50460,6 +50775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51197,6 +51517,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52082,6 +52407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52819,6 +53149,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53704,6 +54039,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54441,6 +54781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55178,6 +55523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56063,6 +56413,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56798,6 +57153,11 @@
       <c r="S382" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO382" t="inlineStr">
